--- a/data/gravel/Tanglefoot Moonshiner 2.0 2025.xlsx
+++ b/data/gravel/Tanglefoot Moonshiner 2.0 2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel not enough data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADD3490-2F24-F849-BBB0-C861A67ECF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03641CA3-1C54-3942-8EFD-BFC890B90C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41160" yWindow="-23720" windowWidth="27960" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33280" yWindow="-23720" windowWidth="27960" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>external</t>
-  </si>
-  <si>
-    <t>not spec'd</t>
   </si>
   <si>
     <t>a8:g36</t>
@@ -857,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -1379,65 +1376,62 @@
         <v>25</v>
       </c>
       <c r="C32" s="1">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="D32" s="1">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="E32" s="1">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="F32" s="1">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="G32" s="1">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>26</v>
       </c>
       <c r="C33">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>2.4</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>27</v>
       </c>
       <c r="C34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="D34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G34">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -1462,7 +1456,7 @@
         <v>187.96</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -1487,7 +1481,7 @@
         <v>203.2</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:7">
       <c r="C37">
         <v>59</v>
       </c>
@@ -1504,7 +1498,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:7">
       <c r="A38" s="1" t="s">
         <v>30</v>
       </c>
@@ -1527,7 +1521,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="21">
+    <row r="39" spans="1:7" ht="21">
       <c r="A39" s="1" t="s">
         <v>68</v>
       </c>
@@ -1540,7 +1534,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:8" ht="21">
+    <row r="40" spans="1:7" ht="21">
       <c r="A40" s="1" t="s">
         <v>69</v>
       </c>
@@ -1553,7 +1547,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
         <v>70</v>
       </c>
@@ -1561,7 +1555,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
@@ -1569,18 +1563,18 @@
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:7">
       <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B43" s="1"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:7">
       <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:7">
       <c r="A45" s="1" t="s">
         <v>36</v>
       </c>
@@ -1588,7 +1582,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
         <v>37</v>
       </c>
@@ -1596,12 +1590,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:7">
       <c r="A47" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:7">
       <c r="A48" s="1" t="s">
         <v>39</v>
       </c>
@@ -1843,7 +1837,7 @@
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tanglefoot Moonshiner 2.0 2025.xlsx
+++ b/data/gravel/Tanglefoot Moonshiner 2.0 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03641CA3-1C54-3942-8EFD-BFC890B90C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF32DC71-4B7E-5C42-B5B6-89130D534E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33280" yWindow="-23720" windowWidth="27960" windowHeight="17460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -407,7 +407,7 @@
     <t>a8:g36</t>
   </si>
   <si>
-    <t>Poultney, Vermont</t>
+    <t>Poultney, Vermont, USA</t>
   </si>
 </sst>
 </file>
